--- a/data/trans_orig/P36A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36A-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la cantidad de agua que consumen al día en 2012</t>
+          <t>Población según la cantidad de agua que consumen al día en 2012 (tasa de respuesta: 98,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>112967</t>
+          <t>111657</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>154170</t>
+          <t>155454</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47016</t>
+          <t>47386</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76130</t>
+          <t>78131</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>168772</t>
+          <t>168064</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>220963</t>
+          <t>221953</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>138311</t>
+          <t>139786</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>183187</t>
+          <t>184829</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>137377</t>
+          <t>136549</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>182675</t>
+          <t>182703</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>287595</t>
+          <t>288233</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>352107</t>
+          <t>352724</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,53%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>199568</t>
+          <t>201814</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>249411</t>
+          <t>253815</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>234239</t>
+          <t>234014</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>405552</t>
+          <t>399334</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>473962</t>
+          <t>471471</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,12%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>110451</t>
+          <t>109501</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>154390</t>
+          <t>152048</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>173665</t>
+          <t>170394</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>222118</t>
+          <t>220120</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>293253</t>
+          <t>295963</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>357220</t>
+          <t>358470</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,94%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33969</t>
+          <t>33464</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>58718</t>
+          <t>59595</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>47050</t>
+          <t>45821</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>78686</t>
+          <t>79303</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>87420</t>
+          <t>87828</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>127641</t>
+          <t>127224</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -1297,97 +1297,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>2055</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>134547</t>
+          <t>134973</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>180558</t>
+          <t>181122</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92288</t>
+          <t>90495</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>134819</t>
+          <t>134028</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>233393</t>
+          <t>236364</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>299960</t>
+          <t>301269</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>208938</t>
+          <t>208113</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>264442</t>
+          <t>266089</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>184597</t>
+          <t>184648</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>237778</t>
+          <t>239946</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>407798</t>
+          <t>410136</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>488504</t>
+          <t>492016</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,31%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>321078</t>
+          <t>321346</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>384779</t>
+          <t>382265</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>305186</t>
+          <t>304498</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>366528</t>
+          <t>366944</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>641412</t>
+          <t>641389</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>727711</t>
+          <t>732337</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,19%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>190350</t>
+          <t>188508</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>243882</t>
+          <t>242335</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>262426</t>
+          <t>261184</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>318951</t>
+          <t>321605</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>467048</t>
+          <t>462899</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>548250</t>
+          <t>546687</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,02%</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32010</t>
+          <t>32694</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>58795</t>
+          <t>58513</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>58111</t>
+          <t>58397</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>93161</t>
+          <t>93956</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>98488</t>
+          <t>96781</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>140340</t>
+          <t>139594</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -2092,97 +2092,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2085</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2107</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2097</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>60275</t>
+          <t>61408</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>98417</t>
+          <t>99662</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>36893</t>
+          <t>35679</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>63942</t>
+          <t>64994</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>105161</t>
+          <t>108236</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>151148</t>
+          <t>153132</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>139333</t>
+          <t>141437</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>186042</t>
+          <t>189163</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>119531</t>
+          <t>120245</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>167785</t>
+          <t>167178</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>273935</t>
+          <t>274900</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>339838</t>
+          <t>339450</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>224429</t>
+          <t>225888</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>277478</t>
+          <t>277441</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>227759</t>
+          <t>229727</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>286532</t>
+          <t>285126</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>469878</t>
+          <t>467070</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>546375</t>
+          <t>547410</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,18%</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>179904</t>
+          <t>179727</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>230202</t>
+          <t>232389</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>216863</t>
+          <t>215182</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>271190</t>
+          <t>271897</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>411926</t>
+          <t>410349</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>485867</t>
+          <t>486804</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,18%</t>
         </is>
       </c>
     </row>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37454</t>
+          <t>36954</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>65339</t>
+          <t>66382</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>61849</t>
+          <t>61020</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>94959</t>
+          <t>95685</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>103692</t>
+          <t>105925</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>148069</t>
+          <t>149426</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -2887,97 +2887,97 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2112</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>2113</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>2115</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>145443</t>
+          <t>143600</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>194452</t>
+          <t>191297</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>130723</t>
+          <t>129310</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>177210</t>
+          <t>175092</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>288180</t>
+          <t>285749</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>354317</t>
+          <t>353189</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,9%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>279780</t>
+          <t>273865</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>338369</t>
+          <t>336602</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>249504</t>
+          <t>250073</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>308890</t>
+          <t>308042</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>542624</t>
+          <t>539371</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>629233</t>
+          <t>626101</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,73%</t>
         </is>
       </c>
     </row>
@@ -3343,12 +3343,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>256766</t>
+          <t>257194</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>311992</t>
+          <t>313111</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3358,12 +3358,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>290826</t>
+          <t>290490</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>348202</t>
+          <t>349902</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>563715</t>
+          <t>561147</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>645441</t>
+          <t>649180</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,89%</t>
         </is>
       </c>
     </row>
@@ -3456,12 +3456,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>117620</t>
+          <t>114763</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>163148</t>
+          <t>160007</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>185522</t>
+          <t>184867</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>235296</t>
+          <t>236092</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>313971</t>
+          <t>312166</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>382179</t>
+          <t>382118</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,36%</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>27179</t>
+          <t>28055</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>52970</t>
+          <t>52679</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>62773</t>
+          <t>63788</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>99230</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3619,12 +3619,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>97021</t>
+          <t>95087</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>140214</t>
+          <t>141465</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -3682,97 +3682,97 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>494568</t>
+          <t>492767</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>585170</t>
+          <t>582855</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>338766</t>
+          <t>334406</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>409365</t>
+          <t>412156</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>851358</t>
+          <t>858305</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>969806</t>
+          <t>968274</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -4025,12 +4025,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>813053</t>
+          <t>815313</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>918112</t>
+          <t>920185</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4040,12 +4040,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4060,12 +4060,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>741441</t>
+          <t>740525</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>848264</t>
+          <t>842023</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4075,12 +4075,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1584050</t>
+          <t>1582330</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1730302</t>
+          <t>1729525</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4110,12 +4110,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -4138,12 +4138,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1058282</t>
+          <t>1052380</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1174107</t>
+          <t>1167818</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1057800</t>
+          <t>1064369</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1176091</t>
+          <t>1177282</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2156258</t>
+          <t>2153640</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2314826</t>
+          <t>2310075</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4223,12 +4223,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,52%</t>
         </is>
       </c>
     </row>
@@ -4251,12 +4251,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>641420</t>
+          <t>643773</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>743193</t>
+          <t>740370</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4266,12 +4266,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>882969</t>
+          <t>882735</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>991576</t>
+          <t>992767</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1552394</t>
+          <t>1556977</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1690418</t>
+          <t>1698646</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -4364,12 +4364,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>153175</t>
+          <t>150858</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>204046</t>
+          <t>203308</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4379,12 +4379,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>257984</t>
+          <t>260005</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>328433</t>
+          <t>328072</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>428439</t>
+          <t>428404</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>512324</t>
+          <t>511732</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4477,97 +4477,97 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>2052</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="R37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>2072</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>2062</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4744,7 +4744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la cantidad de agua que consumen al día en 2016</t>
+          <t>Población según la cantidad de agua que consumen al día en 2016 (tasa de respuesta: 98,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>118138</t>
+          <t>119253</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>161132</t>
+          <t>163236</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55364</t>
+          <t>56526</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>86671</t>
+          <t>87143</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>183240</t>
+          <t>183593</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>236525</t>
+          <t>239910</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>121435</t>
+          <t>120174</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>163211</t>
+          <t>162463</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>135514</t>
+          <t>134819</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>178444</t>
+          <t>178575</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>267783</t>
+          <t>266597</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>329000</t>
+          <t>324920</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,57%</t>
         </is>
       </c>
     </row>
@@ -5165,12 +5165,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>215409</t>
+          <t>215238</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>265819</t>
+          <t>267362</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>221951</t>
+          <t>221359</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>269419</t>
+          <t>270676</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>451964</t>
+          <t>451722</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>523779</t>
+          <t>523939</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,63%</t>
         </is>
       </c>
     </row>
@@ -5278,12 +5278,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88621</t>
+          <t>89926</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>124568</t>
+          <t>128577</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>120027</t>
+          <t>120908</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>161292</t>
+          <t>162470</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>219870</t>
+          <t>218349</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>277794</t>
+          <t>274744</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5391,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23240</t>
+          <t>23680</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46426</t>
+          <t>46966</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36083</t>
+          <t>35446</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>64987</t>
+          <t>61544</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>64131</t>
+          <t>64025</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>99138</t>
+          <t>100778</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -5504,97 +5504,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1982</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1936</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1961</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5734,12 +5734,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>144262</t>
+          <t>145557</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>196247</t>
+          <t>193345</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>123165</t>
+          <t>122710</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>167048</t>
+          <t>166998</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>280012</t>
+          <t>279580</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>350221</t>
+          <t>345635</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -5847,12 +5847,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>277921</t>
+          <t>276633</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>337291</t>
+          <t>335981</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>276500</t>
+          <t>277519</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>339698</t>
+          <t>338677</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>575845</t>
+          <t>572945</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>662146</t>
+          <t>656779</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,67%</t>
         </is>
       </c>
     </row>
@@ -5960,12 +5960,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>303534</t>
+          <t>302279</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>363951</t>
+          <t>364471</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>324395</t>
+          <t>323796</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>385136</t>
+          <t>388926</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>642738</t>
+          <t>641316</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>726603</t>
+          <t>727689</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,2%</t>
         </is>
       </c>
     </row>
@@ -6073,12 +6073,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>117498</t>
+          <t>119544</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>163282</t>
+          <t>163025</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>141386</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>192509</t>
+          <t>191072</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>272775</t>
+          <t>274857</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>340039</t>
+          <t>343537</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,09%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30671</t>
+          <t>29622</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55712</t>
+          <t>53241</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33253</t>
+          <t>34072</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62389</t>
+          <t>62661</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>71595</t>
+          <t>71380</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>107990</t>
+          <t>108085</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -6299,97 +6299,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2060</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2047</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2055</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6529,12 +6529,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>69874</t>
+          <t>70287</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>105054</t>
+          <t>106492</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6564,12 +6564,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>53155</t>
+          <t>52141</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>84392</t>
+          <t>85014</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6599,12 +6599,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>129230</t>
+          <t>133743</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>181053</t>
+          <t>179092</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -6642,12 +6642,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>169042</t>
+          <t>168638</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>215642</t>
+          <t>217597</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6677,12 +6677,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>192444</t>
+          <t>193720</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>245447</t>
+          <t>246232</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6712,12 +6712,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>379618</t>
+          <t>376095</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>447001</t>
+          <t>447383</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,25%</t>
         </is>
       </c>
     </row>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254720</t>
+          <t>252085</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>310730</t>
+          <t>307125</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6790,12 +6790,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>251815</t>
+          <t>258914</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>308758</t>
+          <t>311780</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6825,12 +6825,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>531965</t>
+          <t>524484</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>603503</t>
+          <t>604446</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,52%</t>
         </is>
       </c>
     </row>
@@ -6868,12 +6868,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>146843</t>
+          <t>146496</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>191754</t>
+          <t>194721</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>152881</t>
+          <t>151244</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>201450</t>
+          <t>197298</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6938,12 +6938,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>314016</t>
+          <t>312529</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>380352</t>
+          <t>378919</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -6981,12 +6981,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15732</t>
+          <t>15620</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34845</t>
+          <t>35564</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20561</t>
+          <t>21093</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42318</t>
+          <t>43274</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41406</t>
+          <t>42387</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>72302</t>
+          <t>69959</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -7094,97 +7094,97 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2092</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>2045</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>2070</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7324,12 +7324,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>147655</t>
+          <t>149453</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>191947</t>
+          <t>194821</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7339,12 +7339,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7359,12 +7359,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>118668</t>
+          <t>117389</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>162365</t>
+          <t>164294</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>278110</t>
+          <t>278785</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>345325</t>
+          <t>341305</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,54%</t>
         </is>
       </c>
     </row>
@@ -7437,12 +7437,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>248782</t>
+          <t>250454</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>301804</t>
+          <t>303875</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7452,12 +7452,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7472,12 +7472,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>250171</t>
+          <t>252255</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>307845</t>
+          <t>311430</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>519429</t>
+          <t>515477</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>598364</t>
+          <t>599221</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,79%</t>
         </is>
       </c>
     </row>
@@ -7550,12 +7550,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>263489</t>
+          <t>260833</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>318806</t>
+          <t>320626</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7565,12 +7565,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7585,12 +7585,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>339662</t>
+          <t>337889</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>402613</t>
+          <t>400651</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>617450</t>
+          <t>618404</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>702159</t>
+          <t>702654</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,11%</t>
         </is>
       </c>
     </row>
@@ -7663,12 +7663,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>123552</t>
+          <t>125431</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>168851</t>
+          <t>170666</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7678,12 +7678,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7698,12 +7698,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>168340</t>
+          <t>166883</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>220613</t>
+          <t>218115</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>304815</t>
+          <t>301357</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>374108</t>
+          <t>371903</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,11%</t>
         </is>
       </c>
     </row>
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>23378</t>
+          <t>22765</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>46277</t>
+          <t>47942</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7811,12 +7811,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>39302</t>
+          <t>36884</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>70298</t>
+          <t>67061</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>67176</t>
+          <t>68103</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>104037</t>
+          <t>105236</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -7889,97 +7889,97 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>1930</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>2089</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8119,12 +8119,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>520817</t>
+          <t>518231</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>608111</t>
+          <t>607345</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8154,12 +8154,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>383406</t>
+          <t>383211</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>461581</t>
+          <t>460623</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>924465</t>
+          <t>925652</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1041030</t>
+          <t>1045065</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,35%</t>
         </is>
       </c>
     </row>
@@ -8232,12 +8232,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>865126</t>
+          <t>859251</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>968722</t>
+          <t>964601</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8267,12 +8267,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>909682</t>
+          <t>909997</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1017369</t>
+          <t>1019893</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1807394</t>
+          <t>1800514</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1959330</t>
+          <t>1953475</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -8345,12 +8345,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1090203</t>
+          <t>1093842</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1201102</t>
+          <t>1200438</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8360,12 +8360,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8380,12 +8380,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1193372</t>
+          <t>1194761</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1311552</t>
+          <t>1306690</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8395,12 +8395,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8415,12 +8415,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2319441</t>
+          <t>2323400</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2475672</t>
+          <t>2485403</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8430,12 +8430,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -8458,12 +8458,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>519715</t>
+          <t>524316</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>610450</t>
+          <t>608625</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8473,12 +8473,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>625321</t>
+          <t>627355</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>720715</t>
+          <t>727333</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8508,12 +8508,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8528,12 +8528,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1174686</t>
+          <t>1172756</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1301333</t>
+          <t>1300772</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>111270</t>
+          <t>110244</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>156705</t>
+          <t>153897</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8586,12 +8586,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>148144</t>
+          <t>149670</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>204796</t>
+          <t>202560</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8621,12 +8621,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>275996</t>
+          <t>273379</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>347631</t>
+          <t>343692</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8656,12 +8656,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -8684,97 +8684,97 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="R37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>2039</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la cantidad de agua que consumen al día en 2023</t>
+          <t>Población según la cantidad de agua que consumen al día en 2023 (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9146,12 +9146,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>187441</t>
+          <t>189749</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>243443</t>
+          <t>245750</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9181,12 +9181,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>152079</t>
+          <t>153720</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>189468</t>
+          <t>188168</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>352116</t>
+          <t>354442</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>420000</t>
+          <t>421736</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,51%</t>
         </is>
       </c>
     </row>
@@ -9259,12 +9259,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>193085</t>
+          <t>190788</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>245741</t>
+          <t>244097</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9294,12 +9294,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>228706</t>
+          <t>229846</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>270695</t>
+          <t>268872</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>431712</t>
+          <t>436027</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>497990</t>
+          <t>497695</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,37%</t>
         </is>
       </c>
     </row>
@@ -9372,12 +9372,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>123743</t>
+          <t>123455</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>169725</t>
+          <t>167712</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9387,12 +9387,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>156241</t>
+          <t>155631</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>193075</t>
+          <t>193441</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>293163</t>
+          <t>292395</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>349450</t>
+          <t>346468</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,71%</t>
         </is>
       </c>
     </row>
@@ -9485,12 +9485,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30353</t>
+          <t>29255</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54072</t>
+          <t>53515</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9500,12 +9500,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45063</t>
+          <t>44146</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69281</t>
+          <t>66213</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9535,12 +9535,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79913</t>
+          <t>79048</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113931</t>
+          <t>113652</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9570,12 +9570,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -9598,12 +9598,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6684</t>
+          <t>7045</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17457</t>
+          <t>17513</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9613,12 +9613,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>10191</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23244</t>
+          <t>23495</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9648,12 +9648,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19607</t>
+          <t>20183</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36233</t>
+          <t>36801</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9683,12 +9683,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7094</t>
+          <t>7347</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9761,12 +9761,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8424</t>
+          <t>8556</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -9941,12 +9941,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>339747</t>
+          <t>336071</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>855362</t>
+          <t>880069</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9956,12 +9956,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>176269</t>
+          <t>176161</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>221195</t>
+          <t>222214</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9991,12 +9991,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>521679</t>
+          <t>521174</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1213614</t>
+          <t>1176413</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10026,12 +10026,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>55,1%</t>
         </is>
       </c>
     </row>
@@ -10054,12 +10054,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>169753</t>
+          <t>166672</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>458895</t>
+          <t>460981</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10069,12 +10069,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>337719</t>
+          <t>337517</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>385640</t>
+          <t>390205</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10104,12 +10104,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>461373</t>
+          <t>488104</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>823027</t>
+          <t>823572</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10139,12 +10139,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,57%</t>
         </is>
       </c>
     </row>
@@ -10167,12 +10167,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>117721</t>
+          <t>114336</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>307111</t>
+          <t>307233</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10182,12 +10182,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>246234</t>
+          <t>245220</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>291858</t>
+          <t>292436</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10217,12 +10217,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>329528</t>
+          <t>350000</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>581760</t>
+          <t>582400</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10252,12 +10252,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,28%</t>
         </is>
       </c>
     </row>
@@ -10280,12 +10280,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32085</t>
+          <t>35145</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93689</t>
+          <t>95052</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10295,12 +10295,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>83490</t>
+          <t>85158</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>117124</t>
+          <t>117987</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10330,12 +10330,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>115763</t>
+          <t>113691</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>200730</t>
+          <t>200612</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -10393,12 +10393,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3808</t>
+          <t>3857</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17493</t>
+          <t>17035</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10428,12 +10428,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10975</t>
+          <t>11272</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24873</t>
+          <t>24077</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10443,12 +10443,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10463,12 +10463,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>16390</t>
+          <t>17442</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>36409</t>
+          <t>38101</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10478,12 +10478,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9607</t>
+          <t>7824</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10526,7 +10526,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10541,12 +10541,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>542</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5455</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10561,7 +10561,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11524</t>
+          <t>11645</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10591,12 +10591,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -10736,12 +10736,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>161612</t>
+          <t>161853</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>220887</t>
+          <t>217561</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10751,12 +10751,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10771,12 +10771,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>83908</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>204102</t>
+          <t>203611</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10786,12 +10786,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10806,12 +10806,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>220155</t>
+          <t>216310</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>406099</t>
+          <t>404226</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10821,12 +10821,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -10849,12 +10849,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>210596</t>
+          <t>209323</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>267909</t>
+          <t>269550</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10884,12 +10884,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>131789</t>
+          <t>113886</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>346464</t>
+          <t>339504</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10899,12 +10899,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10919,12 +10919,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>329229</t>
+          <t>324440</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>577627</t>
+          <t>583824</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10934,12 +10934,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,66%</t>
         </is>
       </c>
     </row>
@@ -10962,12 +10962,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>162208</t>
+          <t>161826</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>219035</t>
+          <t>216416</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10977,12 +10977,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10997,12 +10997,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>216032</t>
+          <t>217690</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>639869</t>
+          <t>657958</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11012,12 +11012,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11032,12 +11032,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>412461</t>
+          <t>408790</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>922971</t>
+          <t>986922</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11047,12 +11047,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>60,28%</t>
         </is>
       </c>
     </row>
@@ -11075,12 +11075,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>51211</t>
+          <t>52949</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>86420</t>
+          <t>89038</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11110,12 +11110,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>60592</t>
+          <t>56213</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>156477</t>
+          <t>157424</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11125,12 +11125,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11145,12 +11145,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>118562</t>
+          <t>112911</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>220350</t>
+          <t>217933</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11160,12 +11160,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -11188,12 +11188,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10230</t>
+          <t>9606</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29339</t>
+          <t>29139</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11203,12 +11203,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11223,12 +11223,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16239</t>
+          <t>16153</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50819</t>
+          <t>50684</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11238,12 +11238,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11258,12 +11258,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32697</t>
+          <t>32969</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>69644</t>
+          <t>69060</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11273,12 +11273,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -11301,12 +11301,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9082</t>
+          <t>9248</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11316,12 +11316,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3553</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11356,7 +11356,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11371,12 +11371,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1422</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>10365</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11386,7 +11386,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>213638</t>
+          <t>215716</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>271884</t>
+          <t>273976</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11566,12 +11566,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>148027</t>
+          <t>151748</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>210009</t>
+          <t>210084</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11581,7 +11581,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -11601,12 +11601,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>372534</t>
+          <t>374169</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>466561</t>
+          <t>466455</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11616,12 +11616,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,12%</t>
         </is>
       </c>
     </row>
@@ -11644,12 +11644,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>307527</t>
+          <t>307262</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>372717</t>
+          <t>373774</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11659,12 +11659,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11679,12 +11679,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>272279</t>
+          <t>272675</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>377471</t>
+          <t>379154</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11714,12 +11714,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>601582</t>
+          <t>597064</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>732416</t>
+          <t>731570</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,27%</t>
         </is>
       </c>
     </row>
@@ -11757,12 +11757,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>216759</t>
+          <t>214710</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>275184</t>
+          <t>273731</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11772,12 +11772,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11792,12 +11792,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>314124</t>
+          <t>316945</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>507211</t>
+          <t>530947</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11827,12 +11827,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>551799</t>
+          <t>550723</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>785705</t>
+          <t>782148</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,77%</t>
         </is>
       </c>
     </row>
@@ -11870,12 +11870,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>61758</t>
+          <t>60885</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>93898</t>
+          <t>93072</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11885,12 +11885,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11905,12 +11905,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>121815</t>
+          <t>122193</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>178764</t>
+          <t>177921</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11940,12 +11940,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>198343</t>
+          <t>198653</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>259517</t>
+          <t>259364</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -11983,12 +11983,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12158</t>
+          <t>12069</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28389</t>
+          <t>28280</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11998,12 +11998,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12018,12 +12018,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>26667</t>
+          <t>27032</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>47864</t>
+          <t>48693</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12053,12 +12053,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>42709</t>
+          <t>42459</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>70449</t>
+          <t>69737</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -12096,12 +12096,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>840</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>7374</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12111,12 +12111,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12131,12 +12131,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11146</t>
+          <t>10772</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12166,12 +12166,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>4232</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>14600</t>
+          <t>14374</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -12326,12 +12326,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>979815</t>
+          <t>972993</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1649905</t>
+          <t>1652936</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12341,12 +12341,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12361,12 +12361,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>575027</t>
+          <t>568414</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>770825</t>
+          <t>767525</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1638043</t>
+          <t>1641076</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2494305</t>
+          <t>2629956</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>37,11%</t>
         </is>
       </c>
     </row>
@@ -12439,12 +12439,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>887976</t>
+          <t>873939</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1252447</t>
+          <t>1259851</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12454,12 +12454,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12474,12 +12474,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>958873</t>
+          <t>1004513</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1311543</t>
+          <t>1309802</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12509,12 +12509,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2043882</t>
+          <t>2033645</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2532628</t>
+          <t>2530620</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,71%</t>
         </is>
       </c>
     </row>
@@ -12552,12 +12552,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>625515</t>
+          <t>648397</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>898294</t>
+          <t>897818</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12567,12 +12567,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12587,12 +12587,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1005328</t>
+          <t>1020003</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1694944</t>
+          <t>1639272</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12622,12 +12622,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1784910</t>
+          <t>1776594</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2494484</t>
+          <t>2474844</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>34,92%</t>
         </is>
       </c>
     </row>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>193978</t>
+          <t>199643</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>287856</t>
+          <t>291163</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12680,12 +12680,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12700,12 +12700,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>343934</t>
+          <t>348787</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>467338</t>
+          <t>470099</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12735,12 +12735,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>584250</t>
+          <t>581047</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>739269</t>
+          <t>734265</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -12778,12 +12778,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>40977</t>
+          <t>42326</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>72277</t>
+          <t>74358</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12793,12 +12793,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12813,12 +12813,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>82111</t>
+          <t>80462</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>124322</t>
+          <t>124634</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12848,12 +12848,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>131588</t>
+          <t>130568</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>186513</t>
+          <t>187720</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -12891,12 +12891,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4665</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>16856</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12926,12 +12926,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>18388</t>
+          <t>17124</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12946,7 +12946,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12961,12 +12961,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>13249</t>
+          <t>13513</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>29566</t>
+          <t>29849</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">

--- a/data/trans_orig/P36A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36A-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>111657</t>
+          <t>113142</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>155454</t>
+          <t>157209</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47386</t>
+          <t>46862</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>78131</t>
+          <t>75161</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>168064</t>
+          <t>169987</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>221953</t>
+          <t>222369</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>139786</t>
+          <t>139155</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>184829</t>
+          <t>184026</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>136549</t>
+          <t>134979</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>182703</t>
+          <t>179390</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>288233</t>
+          <t>286041</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>352724</t>
+          <t>350021</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,33%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>201814</t>
+          <t>202812</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>253815</t>
+          <t>253536</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,82 +973,82 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>29,16%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>36,45%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>209001</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>185854</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>234174</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>30,46%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>27,09%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>34,13%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>435833</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>400851</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>472864</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>31,54%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t>29,01%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>36,49%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>209001</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>185533</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>234014</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>30,46%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>27,04%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>34,11%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>435833</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>399334</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>471471</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>31,54%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>28,9%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,22%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>109501</t>
+          <t>109959</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>152048</t>
+          <t>152444</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>170394</t>
+          <t>173910</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>220120</t>
+          <t>223448</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>295963</t>
+          <t>295724</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>358470</t>
+          <t>359115</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33464</t>
+          <t>33701</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>59595</t>
+          <t>58876</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>45821</t>
+          <t>46817</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79303</t>
+          <t>78821</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>87828</t>
+          <t>86506</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>127224</t>
+          <t>126741</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>134973</t>
+          <t>134758</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>181122</t>
+          <t>183267</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>90495</t>
+          <t>90233</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>134028</t>
+          <t>133629</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>236364</t>
+          <t>235283</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>301269</t>
+          <t>299072</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>208113</t>
+          <t>209465</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>266089</t>
+          <t>262442</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>184648</t>
+          <t>184868</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>239946</t>
+          <t>237805</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>410136</t>
+          <t>411941</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>492016</t>
+          <t>489544</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,19%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>321346</t>
+          <t>318783</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>382265</t>
+          <t>381911</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>304498</t>
+          <t>304403</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>366944</t>
+          <t>363655</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>641389</t>
+          <t>642570</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>732337</t>
+          <t>728822</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,02%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>188508</t>
+          <t>188797</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>242335</t>
+          <t>244396</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>261184</t>
+          <t>263760</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>321605</t>
+          <t>322500</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>462899</t>
+          <t>464394</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>546687</t>
+          <t>542059</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,79%</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32694</t>
+          <t>32167</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>58513</t>
+          <t>58608</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>58397</t>
+          <t>58067</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>93956</t>
+          <t>94409</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>96781</t>
+          <t>98202</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>139594</t>
+          <t>141432</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>61408</t>
+          <t>60421</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>99662</t>
+          <t>98508</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>35679</t>
+          <t>36761</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>64994</t>
+          <t>63553</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>108236</t>
+          <t>106222</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>153132</t>
+          <t>152672</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>141437</t>
+          <t>139472</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>189163</t>
+          <t>188057</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>120245</t>
+          <t>120840</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>167178</t>
+          <t>167174</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>274900</t>
+          <t>271796</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>339450</t>
+          <t>336645</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,25%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>225888</t>
+          <t>224890</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>277441</t>
+          <t>276657</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>229727</t>
+          <t>230604</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>285126</t>
+          <t>284893</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>467070</t>
+          <t>471039</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>547410</t>
+          <t>547349</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2661,12 +2661,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>179727</t>
+          <t>180627</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>232389</t>
+          <t>231169</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2676,12 +2676,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>215182</t>
+          <t>217338</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>271897</t>
+          <t>269577</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>410349</t>
+          <t>412704</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>486804</t>
+          <t>483106</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>31,93%</t>
         </is>
       </c>
     </row>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36954</t>
+          <t>35949</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>66382</t>
+          <t>64689</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2789,12 +2789,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>61020</t>
+          <t>61817</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>95685</t>
+          <t>95912</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>105925</t>
+          <t>101730</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>149426</t>
+          <t>149250</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>143600</t>
+          <t>146701</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>191297</t>
+          <t>195405</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>129310</t>
+          <t>127945</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>175092</t>
+          <t>173947</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>285749</t>
+          <t>287694</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>353189</t>
+          <t>348615</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,66%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>273865</t>
+          <t>279132</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>336602</t>
+          <t>338748</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>250073</t>
+          <t>249030</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>308042</t>
+          <t>305273</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>539371</t>
+          <t>545759</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>626101</t>
+          <t>629483</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,9%</t>
         </is>
       </c>
     </row>
@@ -3343,12 +3343,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>257194</t>
+          <t>255303</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>313111</t>
+          <t>310509</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3358,12 +3358,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>290490</t>
+          <t>290622</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>349902</t>
+          <t>349952</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>561147</t>
+          <t>559097</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>649180</t>
+          <t>640296</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,44%</t>
         </is>
       </c>
     </row>
@@ -3456,12 +3456,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>114763</t>
+          <t>116030</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>160007</t>
+          <t>162919</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>184867</t>
+          <t>182536</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>236092</t>
+          <t>235349</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>312166</t>
+          <t>312629</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>382118</t>
+          <t>377774</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,14%</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>28055</t>
+          <t>28124</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>52679</t>
+          <t>52266</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>63788</t>
+          <t>62565</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>99230</t>
+          <t>97923</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3619,12 +3619,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>95087</t>
+          <t>98063</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>141465</t>
+          <t>142715</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>492767</t>
+          <t>492369</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>582855</t>
+          <t>585440</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>334406</t>
+          <t>336936</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>412156</t>
+          <t>413652</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>858305</t>
+          <t>853425</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>968274</t>
+          <t>968718</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -4025,12 +4025,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>815313</t>
+          <t>814292</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>920185</t>
+          <t>921789</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4040,12 +4040,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4060,12 +4060,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>740525</t>
+          <t>744151</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>842023</t>
+          <t>843782</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4075,12 +4075,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1582330</t>
+          <t>1577908</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1729525</t>
+          <t>1729809</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1052380</t>
+          <t>1052553</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1167818</t>
+          <t>1168406</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1064369</t>
+          <t>1060749</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1177282</t>
+          <t>1178058</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2153640</t>
+          <t>2151408</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2310075</t>
+          <t>2308901</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4223,12 +4223,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,5%</t>
         </is>
       </c>
     </row>
@@ -4251,12 +4251,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>643773</t>
+          <t>638955</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>740370</t>
+          <t>735883</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4266,12 +4266,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>882735</t>
+          <t>883624</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>992767</t>
+          <t>996324</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4301,12 +4301,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1556977</t>
+          <t>1554328</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1698646</t>
+          <t>1700378</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,67%</t>
         </is>
       </c>
     </row>
@@ -4364,12 +4364,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>150858</t>
+          <t>148782</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>203308</t>
+          <t>201243</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4379,12 +4379,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>260005</t>
+          <t>260160</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>328072</t>
+          <t>323318</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>428404</t>
+          <t>427222</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>511732</t>
+          <t>511263</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>119253</t>
+          <t>121171</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>163236</t>
+          <t>162810</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4954,82 +4954,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>18,31%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>24,6%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>70634</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>55998</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>88686</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>10,7%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>8,48%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>13,43%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>210146</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>184715</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>238221</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>15,89%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>13,97%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>18,02%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,67%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>70634</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>56526</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>87143</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>10,7%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>8,56%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>13,2%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>210146</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>183593</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>239910</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>15,89%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>13,89%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>120174</t>
+          <t>123861</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>162463</t>
+          <t>165490</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>134819</t>
+          <t>134148</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>178575</t>
+          <t>178460</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>266597</t>
+          <t>267037</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>324920</t>
+          <t>328205</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -5165,12 +5165,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>215238</t>
+          <t>215438</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>267362</t>
+          <t>265317</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>221359</t>
+          <t>222960</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>270676</t>
+          <t>270516</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>451722</t>
+          <t>450695</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>523939</t>
+          <t>519847</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,32%</t>
         </is>
       </c>
     </row>
@@ -5278,12 +5278,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89926</t>
+          <t>91305</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>128577</t>
+          <t>128888</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>120908</t>
+          <t>120847</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>162470</t>
+          <t>161280</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>218349</t>
+          <t>221503</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>274744</t>
+          <t>274748</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5391,12 +5391,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23680</t>
+          <t>22279</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46966</t>
+          <t>45784</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>35446</t>
+          <t>35955</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61544</t>
+          <t>63206</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>64025</t>
+          <t>63752</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>100778</t>
+          <t>99422</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -5734,12 +5734,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>145557</t>
+          <t>143422</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>193345</t>
+          <t>193870</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>122710</t>
+          <t>123601</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166998</t>
+          <t>169008</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>279580</t>
+          <t>280809</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>345635</t>
+          <t>350551</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,44%</t>
         </is>
       </c>
     </row>
@@ -5847,12 +5847,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>276633</t>
+          <t>278541</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>335981</t>
+          <t>338479</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>277519</t>
+          <t>275825</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>338677</t>
+          <t>339099</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>572945</t>
+          <t>577048</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>656779</t>
+          <t>664673</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>33,06%</t>
         </is>
       </c>
     </row>
@@ -5960,12 +5960,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>302279</t>
+          <t>303853</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>364471</t>
+          <t>365779</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>323796</t>
+          <t>322296</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>388926</t>
+          <t>383385</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>641316</t>
+          <t>639820</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>727689</t>
+          <t>732969</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,46%</t>
         </is>
       </c>
     </row>
@@ -6073,12 +6073,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>119544</t>
+          <t>118960</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>163025</t>
+          <t>165285</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>141386</t>
+          <t>144328</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>191072</t>
+          <t>193635</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>274857</t>
+          <t>277674</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>343537</t>
+          <t>340743</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29622</t>
+          <t>31298</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53241</t>
+          <t>54836</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34072</t>
+          <t>33731</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62661</t>
+          <t>62983</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>71380</t>
+          <t>71018</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>108085</t>
+          <t>107160</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -6529,12 +6529,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70287</t>
+          <t>69055</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>106492</t>
+          <t>106599</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6564,12 +6564,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>52141</t>
+          <t>52954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>85014</t>
+          <t>84668</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6599,12 +6599,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>133743</t>
+          <t>132862</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>179092</t>
+          <t>182744</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -6642,12 +6642,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>168638</t>
+          <t>167340</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>217597</t>
+          <t>219911</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6677,12 +6677,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>193720</t>
+          <t>194395</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>246232</t>
+          <t>242702</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6712,12 +6712,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>376095</t>
+          <t>376667</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>447383</t>
+          <t>443236</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>28,98%</t>
         </is>
       </c>
     </row>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252085</t>
+          <t>255793</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>307125</t>
+          <t>308817</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6770,49 +6770,49 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>40,89%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>283839</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>258907</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>314966</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>36,65%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>33,43%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
           <t>40,67%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>283839</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>258914</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>311780</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>36,65%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>33,43%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>40,26%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>527</t>
@@ -6825,12 +6825,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>524484</t>
+          <t>529801</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>604446</t>
+          <t>602585</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,39%</t>
         </is>
       </c>
     </row>
@@ -6868,12 +6868,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>146496</t>
+          <t>147930</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>194721</t>
+          <t>196290</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>151244</t>
+          <t>149478</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>197298</t>
+          <t>197972</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6938,12 +6938,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>312529</t>
+          <t>309182</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>378919</t>
+          <t>376049</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,58%</t>
         </is>
       </c>
     </row>
@@ -6981,12 +6981,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15620</t>
+          <t>15766</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35564</t>
+          <t>34712</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21093</t>
+          <t>21277</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43274</t>
+          <t>43233</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42387</t>
+          <t>41727</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>69959</t>
+          <t>71495</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -7324,12 +7324,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>149453</t>
+          <t>145006</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>194821</t>
+          <t>194482</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7339,12 +7339,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7359,12 +7359,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>117389</t>
+          <t>117206</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>164294</t>
+          <t>166161</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>278785</t>
+          <t>274617</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>341305</t>
+          <t>342085</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -7437,12 +7437,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>250454</t>
+          <t>247016</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>303875</t>
+          <t>301652</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7452,12 +7452,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7472,12 +7472,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>252255</t>
+          <t>253033</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>311430</t>
+          <t>311952</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>515477</t>
+          <t>519203</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>599221</t>
+          <t>598477</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,76%</t>
         </is>
       </c>
     </row>
@@ -7550,12 +7550,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>260833</t>
+          <t>263441</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>320626</t>
+          <t>317210</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7565,12 +7565,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7585,12 +7585,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>337889</t>
+          <t>339502</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>400651</t>
+          <t>402070</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>618404</t>
+          <t>618254</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>702654</t>
+          <t>698538</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,9%</t>
         </is>
       </c>
     </row>
@@ -7663,12 +7663,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>124493</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>170666</t>
+          <t>169389</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7678,12 +7678,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7698,12 +7698,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>166883</t>
+          <t>166511</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>218115</t>
+          <t>220147</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>301357</t>
+          <t>304969</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>371903</t>
+          <t>375848</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>
@@ -7776,12 +7776,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>22765</t>
+          <t>22878</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>47942</t>
+          <t>46522</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7811,12 +7811,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>36884</t>
+          <t>37291</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>67061</t>
+          <t>67206</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>68103</t>
+          <t>66596</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>105236</t>
+          <t>104128</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -8119,12 +8119,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>518231</t>
+          <t>516479</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>607345</t>
+          <t>608099</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8154,12 +8154,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>383211</t>
+          <t>378462</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>460623</t>
+          <t>457765</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>925652</t>
+          <t>921951</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1045065</t>
+          <t>1042058</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,31%</t>
         </is>
       </c>
     </row>
@@ -8232,12 +8232,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>859251</t>
+          <t>867743</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>964601</t>
+          <t>969890</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8267,12 +8267,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>909997</t>
+          <t>907594</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1019893</t>
+          <t>1016908</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1800514</t>
+          <t>1795436</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1953475</t>
+          <t>1952227</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,67%</t>
         </is>
       </c>
     </row>
@@ -8345,12 +8345,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1093842</t>
+          <t>1091101</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1200438</t>
+          <t>1198826</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8360,12 +8360,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8380,12 +8380,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1194761</t>
+          <t>1192241</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1306690</t>
+          <t>1305493</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8395,12 +8395,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8415,12 +8415,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2323400</t>
+          <t>2317498</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2485403</t>
+          <t>2486705</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8430,12 +8430,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,53%</t>
         </is>
       </c>
     </row>
@@ -8458,12 +8458,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>524316</t>
+          <t>523788</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>608625</t>
+          <t>606641</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8473,12 +8473,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>627355</t>
+          <t>628215</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>727333</t>
+          <t>726614</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8508,12 +8508,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8528,12 +8528,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1172756</t>
+          <t>1172503</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1300772</t>
+          <t>1300271</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8543,12 +8543,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -8571,12 +8571,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>110244</t>
+          <t>110276</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>153897</t>
+          <t>156329</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>149670</t>
+          <t>149780</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>202560</t>
+          <t>204566</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8621,12 +8621,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>273379</t>
+          <t>272521</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>343692</t>
+          <t>343128</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8656,12 +8656,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -9141,32 +9141,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>216175</t>
+          <t>242340</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>189749</t>
+          <t>214803</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>245750</t>
+          <t>270616</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9176,32 +9176,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>170313</t>
+          <t>188427</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>153720</t>
+          <t>169275</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>188168</t>
+          <t>208158</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9211,32 +9211,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>386488</t>
+          <t>430768</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>354442</t>
+          <t>394103</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>421736</t>
+          <t>465498</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>33,04%</t>
         </is>
       </c>
     </row>
@@ -9254,32 +9254,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>216594</t>
+          <t>231365</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>190788</t>
+          <t>207984</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>244097</t>
+          <t>257920</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9289,32 +9289,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>248900</t>
+          <t>269939</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>229846</t>
+          <t>249024</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>268872</t>
+          <t>293116</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9324,32 +9324,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>465494</t>
+          <t>501304</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>436027</t>
+          <t>470309</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>497695</t>
+          <t>536681</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,09%</t>
         </is>
       </c>
     </row>
@@ -9367,32 +9367,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>144267</t>
+          <t>155957</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>123455</t>
+          <t>135752</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>167712</t>
+          <t>180896</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9402,32 +9402,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>174361</t>
+          <t>188664</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>155631</t>
+          <t>170568</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>193441</t>
+          <t>207338</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9437,32 +9437,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>318628</t>
+          <t>344622</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>292395</t>
+          <t>315762</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>346468</t>
+          <t>376041</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,69%</t>
         </is>
       </c>
     </row>
@@ -9480,32 +9480,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40563</t>
+          <t>42509</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29255</t>
+          <t>31967</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53515</t>
+          <t>56651</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9515,22 +9515,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>54800</t>
+          <t>57899</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44146</t>
+          <t>47990</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>66213</t>
+          <t>73507</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -9540,7 +9540,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9550,32 +9550,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>95363</t>
+          <t>100408</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79048</t>
+          <t>83976</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113652</t>
+          <t>120138</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -9593,32 +9593,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11508</t>
+          <t>11638</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7045</t>
+          <t>6941</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17513</t>
+          <t>17416</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9628,22 +9628,22 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>15841</t>
+          <t>16424</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10191</t>
+          <t>11083</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23495</t>
+          <t>23226</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9663,32 +9663,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>27348</t>
+          <t>28062</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20183</t>
+          <t>20364</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>36801</t>
+          <t>37167</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -9706,7 +9706,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>808</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>4068</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9741,22 +9741,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3007</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>7230</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9776,32 +9776,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8556</t>
+          <t>8590</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -9819,17 +9819,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>629889</t>
+          <t>684618</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>629889</t>
+          <t>684618</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>629889</t>
+          <t>684618</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9854,17 +9854,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>667221</t>
+          <t>724481</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>667221</t>
+          <t>724481</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>667221</t>
+          <t>724481</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9889,17 +9889,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1297110</t>
+          <t>1409099</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1297110</t>
+          <t>1409099</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1297110</t>
+          <t>1409099</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9936,32 +9936,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>522557</t>
+          <t>324670</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>336071</t>
+          <t>289339</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>880069</t>
+          <t>359345</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9971,32 +9971,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>197633</t>
+          <t>222984</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>176161</t>
+          <t>198499</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>222214</t>
+          <t>246913</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10006,32 +10006,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>720190</t>
+          <t>547654</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>521174</t>
+          <t>506032</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1176413</t>
+          <t>593336</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>28,23%</t>
         </is>
       </c>
     </row>
@@ -10049,32 +10049,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>351740</t>
+          <t>381654</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>166672</t>
+          <t>348083</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>460981</t>
+          <t>417826</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10084,32 +10084,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>362540</t>
+          <t>405472</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>337517</t>
+          <t>377706</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>390205</t>
+          <t>433867</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10119,32 +10119,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>714280</t>
+          <t>787126</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>488104</t>
+          <t>745697</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>823572</t>
+          <t>833549</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>39,65%</t>
         </is>
       </c>
     </row>
@@ -10162,32 +10162,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>233941</t>
+          <t>248911</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>114336</t>
+          <t>221893</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>307233</t>
+          <t>278852</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10197,32 +10197,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>268542</t>
+          <t>297999</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>245220</t>
+          <t>273414</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>292436</t>
+          <t>323040</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10232,32 +10232,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>502483</t>
+          <t>546910</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>350000</t>
+          <t>510976</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>582400</t>
+          <t>583825</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,77%</t>
         </is>
       </c>
     </row>
@@ -10275,32 +10275,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>67841</t>
+          <t>74927</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35145</t>
+          <t>60264</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>95052</t>
+          <t>97360</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10310,32 +10310,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>99577</t>
+          <t>107506</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>85158</t>
+          <t>90658</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>117987</t>
+          <t>125952</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10345,32 +10345,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>167419</t>
+          <t>182433</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>113691</t>
+          <t>158160</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>200612</t>
+          <t>207813</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -10388,67 +10388,67 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9287</t>
+          <t>10886</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>6047</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17035</t>
+          <t>19459</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>22240</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>15145</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>32419</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
           <t>1,43%</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>16983</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>11272</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>24077</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10458,32 +10458,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>26270</t>
+          <t>33126</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>17442</t>
+          <t>23714</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>38101</t>
+          <t>44396</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -10501,7 +10501,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2338</t>
+          <t>2478</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -10511,12 +10511,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7824</t>
+          <t>7856</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -10526,7 +10526,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10536,17 +10536,17 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2388</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>548</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10556,12 +10556,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10571,32 +10571,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4562</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11645</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -10614,17 +10614,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1187704</t>
+          <t>1043525</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1187704</t>
+          <t>1043525</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1187704</t>
+          <t>1043525</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10649,17 +10649,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>947500</t>
+          <t>1058589</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>947500</t>
+          <t>1058589</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>947500</t>
+          <t>1058589</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10684,17 +10684,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2135204</t>
+          <t>2102114</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2135204</t>
+          <t>2102114</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2135204</t>
+          <t>2102114</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10731,32 +10731,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>189519</t>
+          <t>228911</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>161853</t>
+          <t>200805</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>217561</t>
+          <t>261111</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10766,32 +10766,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>150575</t>
+          <t>174705</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>154994</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>203611</t>
+          <t>198767</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10801,32 +10801,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>340094</t>
+          <t>403616</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>216310</t>
+          <t>367775</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>404226</t>
+          <t>445209</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>27,58%</t>
         </is>
       </c>
     </row>
@@ -10844,32 +10844,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>237214</t>
+          <t>261027</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>209323</t>
+          <t>230878</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>269550</t>
+          <t>292506</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10879,32 +10879,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>248093</t>
+          <t>251274</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>113886</t>
+          <t>227262</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>339504</t>
+          <t>275853</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10914,32 +10914,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>485308</t>
+          <t>512300</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>324440</t>
+          <t>475310</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>583824</t>
+          <t>554835</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>34,37%</t>
         </is>
       </c>
     </row>
@@ -10957,32 +10957,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>190892</t>
+          <t>218554</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>161826</t>
+          <t>188316</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>216416</t>
+          <t>247565</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10992,32 +10992,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>384493</t>
+          <t>213219</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>217690</t>
+          <t>190182</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>657958</t>
+          <t>238522</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11027,32 +11027,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>575385</t>
+          <t>431773</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>408790</t>
+          <t>393391</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>986922</t>
+          <t>469925</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>29,11%</t>
         </is>
       </c>
     </row>
@@ -11070,32 +11070,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>66874</t>
+          <t>73394</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>52949</t>
+          <t>57396</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>89038</t>
+          <t>95480</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11105,32 +11105,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>114432</t>
+          <t>133156</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>56213</t>
+          <t>115609</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>157424</t>
+          <t>152353</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11140,32 +11140,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>181306</t>
+          <t>206551</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>112911</t>
+          <t>179186</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>217933</t>
+          <t>233499</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -11183,32 +11183,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>16618</t>
+          <t>17249</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9606</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29139</t>
+          <t>29806</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11218,32 +11218,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>34357</t>
+          <t>38342</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16153</t>
+          <t>27951</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50684</t>
+          <t>51413</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11253,32 +11253,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>50975</t>
+          <t>55591</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32969</t>
+          <t>42412</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>69060</t>
+          <t>71266</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -11296,32 +11296,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3564</t>
+          <t>3938</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9248</t>
+          <t>9777</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11331,7 +11331,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>709</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -11341,12 +11341,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>3589</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -11356,7 +11356,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11366,32 +11366,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>4228</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>1715</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>10351</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -11409,17 +11409,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11444,17 +11444,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>932614</t>
+          <t>811405</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>932614</t>
+          <t>811405</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>932614</t>
+          <t>811405</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11479,17 +11479,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1637295</t>
+          <t>1614478</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1637295</t>
+          <t>1614478</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1637295</t>
+          <t>1614478</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11526,27 +11526,27 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>242110</t>
+          <t>262710</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>215716</t>
+          <t>231358</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>273976</t>
+          <t>292707</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -11561,32 +11561,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>184023</t>
+          <t>201363</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>151748</t>
+          <t>180309</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>210084</t>
+          <t>226278</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11596,32 +11596,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>426134</t>
+          <t>464073</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>374169</t>
+          <t>427156</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>466455</t>
+          <t>503731</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,94%</t>
         </is>
       </c>
     </row>
@@ -11639,32 +11639,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>340706</t>
+          <t>357052</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>307262</t>
+          <t>326365</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>373774</t>
+          <t>394350</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11674,32 +11674,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>343595</t>
+          <t>379268</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>272675</t>
+          <t>351275</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>379154</t>
+          <t>407726</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11709,32 +11709,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>684301</t>
+          <t>736320</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>597064</t>
+          <t>688839</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>731570</t>
+          <t>776984</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,93%</t>
         </is>
       </c>
     </row>
@@ -11752,32 +11752,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>243533</t>
+          <t>263828</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>214710</t>
+          <t>232602</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>273731</t>
+          <t>295098</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11787,32 +11787,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>372858</t>
+          <t>331220</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>316945</t>
+          <t>303394</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>530947</t>
+          <t>357931</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11822,32 +11822,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>616392</t>
+          <t>595048</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>550723</t>
+          <t>559106</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>782148</t>
+          <t>636581</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>30,26%</t>
         </is>
       </c>
     </row>
@@ -11865,32 +11865,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>75693</t>
+          <t>81041</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>60885</t>
+          <t>66188</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>93072</t>
+          <t>98336</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11900,32 +11900,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>151960</t>
+          <t>158109</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>122193</t>
+          <t>136994</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>177921</t>
+          <t>178888</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11935,27 +11935,27 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>227653</t>
+          <t>239150</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>198653</t>
+          <t>215517</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>259364</t>
+          <t>270663</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -11978,32 +11978,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>18649</t>
+          <t>19385</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12069</t>
+          <t>11775</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28280</t>
+          <t>29084</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12013,32 +12013,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>36078</t>
+          <t>40960</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>27032</t>
+          <t>30209</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>48693</t>
+          <t>52423</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12048,32 +12048,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>54727</t>
+          <t>60345</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>42459</t>
+          <t>48099</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>69737</t>
+          <t>75773</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -12091,32 +12091,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2899</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>839</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7374</t>
+          <t>7543</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12126,32 +12126,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>4992</t>
+          <t>6156</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>10772</t>
+          <t>11947</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12161,32 +12161,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>9054</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>4571</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>14374</t>
+          <t>15256</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -12204,17 +12204,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>923720</t>
+          <t>986914</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>923720</t>
+          <t>986914</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>923720</t>
+          <t>986914</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -12239,17 +12239,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1093506</t>
+          <t>1117076</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1093506</t>
+          <t>1117076</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1093506</t>
+          <t>1117076</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -12274,17 +12274,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>2017227</t>
+          <t>2103991</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2017227</t>
+          <t>2103991</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2017227</t>
+          <t>2103991</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -12321,32 +12321,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1170362</t>
+          <t>1058632</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>972993</t>
+          <t>995524</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1652936</t>
+          <t>1122920</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12356,32 +12356,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>702543</t>
+          <t>787479</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>568414</t>
+          <t>743250</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>767525</t>
+          <t>833541</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12391,32 +12391,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1872906</t>
+          <t>1846111</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1641076</t>
+          <t>1769563</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2629956</t>
+          <t>1930076</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>26,7%</t>
         </is>
       </c>
     </row>
@@ -12434,32 +12434,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1146254</t>
+          <t>1231097</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>873939</t>
+          <t>1171725</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1259851</t>
+          <t>1298282</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12469,32 +12469,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1203128</t>
+          <t>1305953</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1004513</t>
+          <t>1253577</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1309802</t>
+          <t>1357862</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12504,32 +12504,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>2349382</t>
+          <t>2537050</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2033645</t>
+          <t>2452977</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2530620</t>
+          <t>2614991</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>36,17%</t>
         </is>
       </c>
     </row>
@@ -12547,32 +12547,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>812634</t>
+          <t>887250</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>648397</t>
+          <t>830570</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>897818</t>
+          <t>943991</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12582,32 +12582,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1200253</t>
+          <t>1031102</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1020003</t>
+          <t>985746</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1639272</t>
+          <t>1081300</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12617,32 +12617,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>2012887</t>
+          <t>1918353</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1776594</t>
+          <t>1843604</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2474844</t>
+          <t>1992024</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>27,55%</t>
         </is>
       </c>
     </row>
@@ -12660,32 +12660,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>250970</t>
+          <t>271870</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>199643</t>
+          <t>236946</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>291163</t>
+          <t>305961</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12695,32 +12695,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>420769</t>
+          <t>456670</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>348787</t>
+          <t>422692</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>470099</t>
+          <t>494343</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12730,32 +12730,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>671739</t>
+          <t>728541</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>581047</t>
+          <t>678339</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>734265</t>
+          <t>778195</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,76%</t>
         </is>
       </c>
     </row>
@@ -12773,32 +12773,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>56062</t>
+          <t>59157</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>42326</t>
+          <t>45098</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>74358</t>
+          <t>76181</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12808,32 +12808,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>103259</t>
+          <t>117966</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>80462</t>
+          <t>98575</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>124634</t>
+          <t>140270</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12843,32 +12843,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>159320</t>
+          <t>177123</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>130568</t>
+          <t>154857</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>187720</t>
+          <t>204868</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -12886,22 +12886,22 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>10123</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>17682</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -12911,7 +12911,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12921,32 +12921,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>10889</t>
+          <t>12381</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>6177</t>
+          <t>7345</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>17124</t>
+          <t>19448</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12956,32 +12956,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>20601</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>13513</t>
+          <t>14794</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>29849</t>
+          <t>32560</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -12999,17 +12999,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3445994</t>
+          <t>3518130</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3445994</t>
+          <t>3518130</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3445994</t>
+          <t>3518130</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13034,17 +13034,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3640841</t>
+          <t>3711551</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3640841</t>
+          <t>3711551</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3640841</t>
+          <t>3711551</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13069,17 +13069,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>7086835</t>
+          <t>7229681</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>7086835</t>
+          <t>7229681</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>7086835</t>
+          <t>7229681</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
